--- a/mapfre.xlsx
+++ b/mapfre.xlsx
@@ -1,34 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\COTIZADOR SOAT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C77234-48BA-41FB-9AC3-EBCAE260E7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBFC78E-3F22-40C0-8171-0AD673453C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{5A05F6F8-2926-42A3-AE35-387DBB0B8114}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5A05F6F8-2926-42A3-AE35-387DBB0B8114}"/>
   </bookViews>
   <sheets>
     <sheet name="TARIFARIO" sheetId="2" r:id="rId1"/>
     <sheet name="GRUPOS" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2228,61 +2219,61 @@
         <v>149</v>
       </c>
       <c r="G14">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="H14">
+        <v>350</v>
+      </c>
+      <c r="I14">
+        <v>450</v>
+      </c>
+      <c r="J14">
+        <v>320</v>
+      </c>
+      <c r="K14">
         <v>400</v>
-      </c>
-      <c r="I14">
-        <v>300</v>
-      </c>
-      <c r="J14">
-        <v>400</v>
-      </c>
-      <c r="K14">
-        <v>320</v>
       </c>
       <c r="L14">
         <v>320</v>
       </c>
       <c r="M14">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="N14">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="O14">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="P14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="Q14">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="R14">
+        <v>335</v>
+      </c>
+      <c r="S14">
+        <v>750</v>
+      </c>
+      <c r="T14">
+        <v>450</v>
+      </c>
+      <c r="U14">
         <v>320</v>
-      </c>
-      <c r="S14">
-        <v>700</v>
-      </c>
-      <c r="T14">
-        <v>400</v>
-      </c>
-      <c r="U14">
-        <v>300</v>
       </c>
       <c r="V14">
         <v>350</v>
       </c>
       <c r="W14">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="X14">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="Y14">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="Z14">
         <v>360</v>
@@ -2291,13 +2282,13 @@
         <v>300</v>
       </c>
       <c r="AB14">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AC14">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AD14">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -2317,61 +2308,61 @@
         <v>149</v>
       </c>
       <c r="G15">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="H15">
+        <v>400</v>
+      </c>
+      <c r="I15">
+        <v>500</v>
+      </c>
+      <c r="J15">
+        <v>370</v>
+      </c>
+      <c r="K15">
         <v>450</v>
-      </c>
-      <c r="I15">
-        <v>350</v>
-      </c>
-      <c r="J15">
-        <v>450</v>
-      </c>
-      <c r="K15">
-        <v>370</v>
       </c>
       <c r="L15">
         <v>370</v>
       </c>
       <c r="M15">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="N15">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="O15">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="P15">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="Q15">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="R15">
+        <v>385</v>
+      </c>
+      <c r="S15">
+        <v>800</v>
+      </c>
+      <c r="T15">
+        <v>500</v>
+      </c>
+      <c r="U15">
         <v>370</v>
-      </c>
-      <c r="S15">
-        <v>750</v>
-      </c>
-      <c r="T15">
-        <v>450</v>
-      </c>
-      <c r="U15">
-        <v>350</v>
       </c>
       <c r="V15">
         <v>400</v>
       </c>
       <c r="W15">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="X15">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="Y15">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Z15">
         <v>410</v>
@@ -2380,13 +2371,13 @@
         <v>350</v>
       </c>
       <c r="AB15">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AC15">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AD15">
-        <v>370</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -2406,22 +2397,22 @@
         <v>149</v>
       </c>
       <c r="G16">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="H16">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="I16">
-        <v>285</v>
+        <v>415</v>
       </c>
       <c r="J16">
         <v>385</v>
       </c>
       <c r="K16">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="L16">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="M16">
         <v>355</v>
@@ -2430,7 +2421,7 @@
         <v>245</v>
       </c>
       <c r="O16">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="P16">
         <v>285</v>
@@ -2439,43 +2430,43 @@
         <v>285</v>
       </c>
       <c r="R16">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="S16">
-        <v>685</v>
+        <v>715</v>
       </c>
       <c r="T16">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="U16">
         <v>285</v>
       </c>
       <c r="V16">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="W16">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="X16">
         <v>335</v>
       </c>
       <c r="Y16">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="Z16">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="AA16">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="AB16">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="AC16">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="AD16">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -2495,76 +2486,76 @@
         <v>149</v>
       </c>
       <c r="G17">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="H17">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="I17">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="J17">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="K17">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="L17">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="M17">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="N17">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="O17">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="P17">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="Q17">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="R17">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="S17">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="T17">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="U17">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="V17">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="W17">
         <v>310</v>
       </c>
       <c r="X17">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="Y17">
         <v>310</v>
       </c>
       <c r="Z17">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AA17">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB17">
         <v>310</v>
       </c>
       <c r="AC17">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AD17">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -2584,61 +2575,61 @@
         <v>149</v>
       </c>
       <c r="G18">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="H18">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="I18">
         <v>300</v>
       </c>
       <c r="J18">
+        <v>320</v>
+      </c>
+      <c r="K18">
         <v>400</v>
-      </c>
-      <c r="K18">
-        <v>320</v>
       </c>
       <c r="L18">
         <v>320</v>
       </c>
       <c r="M18">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="N18">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="O18">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="P18">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="Q18">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="R18">
+        <v>335</v>
+      </c>
+      <c r="S18">
+        <v>750</v>
+      </c>
+      <c r="T18">
+        <v>450</v>
+      </c>
+      <c r="U18">
         <v>320</v>
-      </c>
-      <c r="S18">
-        <v>700</v>
-      </c>
-      <c r="T18">
-        <v>400</v>
-      </c>
-      <c r="U18">
-        <v>300</v>
       </c>
       <c r="V18">
         <v>350</v>
       </c>
       <c r="W18">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="X18">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="Y18">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="Z18">
         <v>360</v>
@@ -2647,13 +2638,13 @@
         <v>300</v>
       </c>
       <c r="AB18">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="AC18">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AD18">
-        <v>320</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -3833,61 +3824,61 @@
         <v>149</v>
       </c>
       <c r="G32">
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="H32">
+        <v>400</v>
+      </c>
+      <c r="I32">
+        <v>500</v>
+      </c>
+      <c r="J32">
+        <v>370</v>
+      </c>
+      <c r="K32">
         <v>450</v>
-      </c>
-      <c r="I32">
-        <v>350</v>
-      </c>
-      <c r="J32">
-        <v>450</v>
-      </c>
-      <c r="K32">
-        <v>370</v>
       </c>
       <c r="L32">
         <v>370</v>
       </c>
       <c r="M32">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="N32">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="O32">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="P32">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="Q32">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="R32">
+        <v>385</v>
+      </c>
+      <c r="S32">
+        <v>800</v>
+      </c>
+      <c r="T32">
+        <v>500</v>
+      </c>
+      <c r="U32">
         <v>370</v>
-      </c>
-      <c r="S32">
-        <v>750</v>
-      </c>
-      <c r="T32">
-        <v>450</v>
-      </c>
-      <c r="U32">
-        <v>350</v>
       </c>
       <c r="V32">
         <v>400</v>
       </c>
       <c r="W32">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="X32">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="Y32">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Z32">
         <v>410</v>
@@ -3896,13 +3887,13 @@
         <v>350</v>
       </c>
       <c r="AB32">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AC32">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="AD32">
-        <v>370</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
@@ -3922,76 +3913,76 @@
         <v>149</v>
       </c>
       <c r="G33">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="H33">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="I33">
-        <v>400</v>
+        <v>540</v>
       </c>
       <c r="J33">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="K33">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="L33">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="M33">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="N33">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="O33">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="P33">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="Q33">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R33">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="S33">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="T33">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="U33">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="V33">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="W33">
         <v>420</v>
       </c>
       <c r="X33">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="Y33">
         <v>420</v>
       </c>
       <c r="Z33">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AA33">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="AB33">
         <v>420</v>
       </c>
       <c r="AC33">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AD33">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
@@ -4011,76 +4002,76 @@
         <v>149</v>
       </c>
       <c r="G34">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="H34">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="I34">
-        <v>320</v>
+        <v>460</v>
       </c>
       <c r="J34">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="K34">
-        <v>340</v>
+        <v>410</v>
       </c>
       <c r="L34">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="M34">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="N34">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="O34">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="P34">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="Q34">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="R34">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="S34">
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="T34">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="U34">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="V34">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="W34">
         <v>340</v>
       </c>
       <c r="X34">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Y34">
         <v>340</v>
       </c>
       <c r="Z34">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AA34">
-        <v>320</v>
+        <v>370</v>
       </c>
       <c r="AB34">
         <v>340</v>
       </c>
       <c r="AC34">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AD34">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/mapfre.xlsx
+++ b/mapfre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBFC78E-3F22-40C0-8171-0AD673453C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8698407C-90BD-44F6-B99D-6DBE153AD58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5A05F6F8-2926-42A3-AE35-387DBB0B8114}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{5A05F6F8-2926-42A3-AE35-387DBB0B8114}"/>
   </bookViews>
   <sheets>
     <sheet name="TARIFARIO" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1089" uniqueCount="231">
   <si>
     <t>USO</t>
   </si>
@@ -214,9 +214,6 @@
     <t>PANEL</t>
   </si>
   <si>
-    <t>TRIMOTO</t>
-  </si>
-  <si>
     <t>SUV, MULTIPROPOSITO</t>
   </si>
   <si>
@@ -505,9 +502,6 @@
     <t>HAOJUE</t>
   </si>
   <si>
-    <t>IGM</t>
-  </si>
-  <si>
     <t>ITALIKA</t>
   </si>
   <si>
@@ -526,9 +520,6 @@
     <t>ROBBIRA MOTOS</t>
   </si>
   <si>
-    <t>RTM</t>
-  </si>
-  <si>
     <t>SENKE</t>
   </si>
   <si>
@@ -599,6 +590,135 @@
   </si>
   <si>
     <t>SUV, MULTIPROPOSITO, VAN</t>
+  </si>
+  <si>
+    <t>Accent</t>
+  </si>
+  <si>
+    <t>Cerato</t>
+  </si>
+  <si>
+    <t>Soluto</t>
+  </si>
+  <si>
+    <t>Sentra</t>
+  </si>
+  <si>
+    <t>Versa</t>
+  </si>
+  <si>
+    <t>Tiida</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Mazda 3</t>
+  </si>
+  <si>
+    <t>Tico</t>
+  </si>
+  <si>
+    <t>BARSHA</t>
+  </si>
+  <si>
+    <t>BOSUER</t>
+  </si>
+  <si>
+    <t>FURBO</t>
+  </si>
+  <si>
+    <t>FX RIDE</t>
+  </si>
+  <si>
+    <t>GREENLINE</t>
+  </si>
+  <si>
+    <t>JAPON MOTOS</t>
+  </si>
+  <si>
+    <t>LIFAN</t>
+  </si>
+  <si>
+    <t>LINHAI</t>
+  </si>
+  <si>
+    <t>MAQUIMOTO</t>
+  </si>
+  <si>
+    <t>NEDSO</t>
+  </si>
+  <si>
+    <t>PLUSONE</t>
+  </si>
+  <si>
+    <t>PREMIER</t>
+  </si>
+  <si>
+    <t>REZZIO</t>
+  </si>
+  <si>
+    <t>SEMZA</t>
+  </si>
+  <si>
+    <t>WOOMBER</t>
+  </si>
+  <si>
+    <t>YANGZU</t>
+  </si>
+  <si>
+    <t>ZONGSHEN</t>
+  </si>
+  <si>
+    <t>BIG TONY</t>
+  </si>
+  <si>
+    <t>GUZZI</t>
+  </si>
+  <si>
+    <t>Probox</t>
+  </si>
+  <si>
+    <t>Avanza</t>
+  </si>
+  <si>
+    <t>Rush</t>
+  </si>
+  <si>
+    <t>Raize</t>
+  </si>
+  <si>
+    <t>Xpander</t>
+  </si>
+  <si>
+    <t>Tiggo</t>
+  </si>
+  <si>
+    <t>Cs15</t>
+  </si>
+  <si>
+    <t>X70</t>
+  </si>
+  <si>
+    <t>Sx6</t>
+  </si>
+  <si>
+    <t>Terios</t>
+  </si>
+  <si>
+    <t>JETOUR</t>
+  </si>
+  <si>
+    <t>DAIHATSU</t>
+  </si>
+  <si>
+    <t>Glory 560</t>
+  </si>
+  <si>
+    <t>Ad</t>
+  </si>
+  <si>
+    <t>TRIMOTO, FURGONETA</t>
   </si>
 </sst>
 </file>
@@ -703,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -725,6 +845,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1039,8 +1163,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024CB55F-92EB-4EB0-AA73-FC2CD4A1FE77}">
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="6" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1252,7 +1379,7 @@
         <v>69</v>
       </c>
       <c r="K3">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L3">
         <v>79</v>
@@ -1264,7 +1391,7 @@
         <v>150</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P3">
         <v>90</v>
@@ -1276,7 +1403,7 @@
         <v>92</v>
       </c>
       <c r="S3">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T3">
         <v>70</v>
@@ -1294,10 +1421,10 @@
         <v>90</v>
       </c>
       <c r="Y3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Z3">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="AA3">
         <v>69</v>
@@ -1309,7 +1436,7 @@
         <v>69</v>
       </c>
       <c r="AD3">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
@@ -1353,13 +1480,13 @@
         <v>69</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="P4">
         <v>89</v>
       </c>
       <c r="Q4">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="R4">
         <v>220</v>
@@ -1368,7 +1495,7 @@
         <v>76</v>
       </c>
       <c r="T4">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U4">
         <v>69</v>
@@ -1398,7 +1525,7 @@
         <v>69</v>
       </c>
       <c r="AD4">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1418,13 +1545,13 @@
         <v>34</v>
       </c>
       <c r="G5">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="H5">
         <v>200</v>
       </c>
       <c r="I5">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="J5">
         <v>200</v>
@@ -1454,7 +1581,7 @@
         <v>200</v>
       </c>
       <c r="S5">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="T5">
         <v>200</v>
@@ -1475,7 +1602,7 @@
         <v>200</v>
       </c>
       <c r="Z5">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AA5">
         <v>200</v>
@@ -1487,7 +1614,7 @@
         <v>200</v>
       </c>
       <c r="AD5">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
@@ -1507,7 +1634,7 @@
         <v>34</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="H6">
         <v>70</v>
@@ -1519,7 +1646,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="L6">
         <v>85</v>
@@ -1528,28 +1655,28 @@
         <v>95</v>
       </c>
       <c r="N6">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="R6">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="S6">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="U6">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V6">
         <v>70</v>
@@ -1570,13 +1697,13 @@
         <v>69</v>
       </c>
       <c r="AB6">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="AC6">
         <v>69</v>
       </c>
       <c r="AD6">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
@@ -1596,7 +1723,7 @@
         <v>34</v>
       </c>
       <c r="G7">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H7">
         <v>70</v>
@@ -1608,13 +1735,13 @@
         <v>69</v>
       </c>
       <c r="K7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L7">
         <v>79</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N7">
         <v>69</v>
@@ -1626,19 +1753,19 @@
         <v>220</v>
       </c>
       <c r="Q7">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="R7">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="S7">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T7">
         <v>70</v>
       </c>
       <c r="U7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="V7">
         <v>70</v>
@@ -1647,7 +1774,7 @@
         <v>70</v>
       </c>
       <c r="X7">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Y7">
         <v>68</v>
@@ -1656,7 +1783,7 @@
         <v>69</v>
       </c>
       <c r="AA7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AB7">
         <v>70</v>
@@ -1685,7 +1812,7 @@
         <v>34</v>
       </c>
       <c r="G8">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="H8">
         <v>70</v>
@@ -1694,19 +1821,19 @@
         <v>84</v>
       </c>
       <c r="J8">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="K8">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L8">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="M8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N8">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="O8">
         <v>90</v>
@@ -1715,13 +1842,13 @@
         <v>89</v>
       </c>
       <c r="Q8">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="R8">
         <v>92</v>
       </c>
       <c r="S8">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T8">
         <v>70</v>
@@ -1733,7 +1860,7 @@
         <v>70</v>
       </c>
       <c r="W8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X8">
         <v>90</v>
@@ -1742,13 +1869,13 @@
         <v>68</v>
       </c>
       <c r="Z8">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AA8">
         <v>69</v>
       </c>
       <c r="AB8">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC8">
         <v>69</v>
@@ -1774,7 +1901,7 @@
         <v>34</v>
       </c>
       <c r="G9">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H9">
         <v>70</v>
@@ -1786,7 +1913,7 @@
         <v>69</v>
       </c>
       <c r="K9">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L9">
         <v>79</v>
@@ -1795,7 +1922,7 @@
         <v>70</v>
       </c>
       <c r="N9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="O9">
         <v>90</v>
@@ -1804,13 +1931,13 @@
         <v>89</v>
       </c>
       <c r="Q9">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="R9">
         <v>92</v>
       </c>
       <c r="S9">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T9">
         <v>70</v>
@@ -1831,7 +1958,7 @@
         <v>68</v>
       </c>
       <c r="Z9">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AA9">
         <v>69</v>
@@ -1863,10 +1990,10 @@
         <v>34</v>
       </c>
       <c r="G10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I10">
         <v>84</v>
@@ -1875,10 +2002,10 @@
         <v>69</v>
       </c>
       <c r="K10">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L10">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M10">
         <v>70</v>
@@ -1893,16 +2020,16 @@
         <v>89</v>
       </c>
       <c r="Q10">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>92</v>
       </c>
       <c r="S10">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T10">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U10">
         <v>69</v>
@@ -1917,7 +2044,7 @@
         <v>90</v>
       </c>
       <c r="Y10">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="Z10">
         <v>69</v>
@@ -1952,28 +2079,28 @@
         <v>34</v>
       </c>
       <c r="G11">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I11">
+        <v>84</v>
+      </c>
+      <c r="J11">
+        <v>69</v>
+      </c>
+      <c r="K11">
+        <v>85</v>
+      </c>
+      <c r="L11">
+        <v>85</v>
+      </c>
+      <c r="M11">
+        <v>70</v>
+      </c>
+      <c r="N11">
         <v>90</v>
-      </c>
-      <c r="J11">
-        <v>69</v>
-      </c>
-      <c r="K11">
-        <v>69</v>
-      </c>
-      <c r="L11">
-        <v>79</v>
-      </c>
-      <c r="M11">
-        <v>70</v>
-      </c>
-      <c r="N11">
-        <v>69</v>
       </c>
       <c r="O11">
         <v>90</v>
@@ -1982,13 +2109,13 @@
         <v>89</v>
       </c>
       <c r="Q11">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="R11">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="S11">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="T11">
         <v>70</v>
@@ -2006,7 +2133,7 @@
         <v>90</v>
       </c>
       <c r="Y11">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="Z11">
         <v>69</v>
@@ -2041,28 +2168,28 @@
         <v>34</v>
       </c>
       <c r="G12">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H12">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I12">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J12">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="L12">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M12">
         <v>70</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="O12">
         <v>90</v>
@@ -2071,13 +2198,13 @@
         <v>89</v>
       </c>
       <c r="Q12">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="R12">
         <v>92</v>
       </c>
       <c r="S12">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="T12">
         <v>70</v>
@@ -2130,28 +2257,28 @@
         <v>34</v>
       </c>
       <c r="G13">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J13">
         <v>69</v>
       </c>
       <c r="K13">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="L13">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M13">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="O13">
         <v>90</v>
@@ -2160,13 +2287,13 @@
         <v>89</v>
       </c>
       <c r="Q13">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="R13">
         <v>92</v>
       </c>
       <c r="S13">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="T13">
         <v>70</v>
@@ -2184,7 +2311,7 @@
         <v>90</v>
       </c>
       <c r="Y13">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="Z13">
         <v>69</v>
@@ -2207,88 +2334,88 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>148</v>
-      </c>
-      <c r="C14" s="10">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D14" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D14">
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G14">
-        <v>595</v>
+        <v>110</v>
       </c>
       <c r="H14">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="I14">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="J14">
-        <v>320</v>
+        <v>71</v>
       </c>
       <c r="K14">
-        <v>400</v>
+        <v>67</v>
       </c>
       <c r="L14">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="M14">
-        <v>390</v>
+        <v>68</v>
       </c>
       <c r="N14">
-        <v>280</v>
+        <v>90</v>
       </c>
       <c r="O14">
-        <v>400</v>
+        <v>89</v>
       </c>
       <c r="P14">
-        <v>320</v>
+        <v>89</v>
       </c>
       <c r="Q14">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="R14">
-        <v>335</v>
+        <v>95</v>
       </c>
       <c r="S14">
-        <v>750</v>
+        <v>76</v>
       </c>
       <c r="T14">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="U14">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="V14">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="W14">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="X14">
-        <v>370</v>
+        <v>90</v>
       </c>
       <c r="Y14">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="Z14">
-        <v>360</v>
+        <v>71</v>
       </c>
       <c r="AA14">
-        <v>300</v>
+        <v>69</v>
       </c>
       <c r="AB14">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="AC14">
-        <v>350</v>
+        <v>69</v>
       </c>
       <c r="AD14">
-        <v>350</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
@@ -2296,88 +2423,88 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C15" s="10">
-        <v>7.4999999999999997E-2</v>
+        <v>7</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.15</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G15">
-        <v>720</v>
+        <v>190</v>
       </c>
       <c r="H15">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="I15">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="J15">
-        <v>370</v>
+        <v>69</v>
       </c>
       <c r="K15">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="L15">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="M15">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="N15">
-        <v>330</v>
+        <v>69</v>
       </c>
       <c r="O15">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="P15">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="Q15">
-        <v>370</v>
+        <v>74</v>
       </c>
       <c r="R15">
-        <v>385</v>
+        <v>95</v>
       </c>
       <c r="S15">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="T15">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="U15">
-        <v>370</v>
+        <v>69</v>
       </c>
       <c r="V15">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="W15">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="X15">
-        <v>420</v>
+        <v>90</v>
       </c>
       <c r="Y15">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="Z15">
-        <v>410</v>
+        <v>69</v>
       </c>
       <c r="AA15">
-        <v>350</v>
+        <v>69</v>
       </c>
       <c r="AB15">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="AC15">
-        <v>400</v>
+        <v>69</v>
       </c>
       <c r="AD15">
-        <v>400</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
@@ -2385,88 +2512,88 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="10">
-        <v>7.4999999999999997E-2</v>
+        <v>7</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.15</v>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G16">
-        <v>550</v>
+        <v>120</v>
       </c>
       <c r="H16">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="I16">
-        <v>415</v>
+        <v>93</v>
       </c>
       <c r="J16">
-        <v>385</v>
+        <v>69</v>
       </c>
       <c r="K16">
-        <v>365</v>
+        <v>95</v>
       </c>
       <c r="L16">
-        <v>285</v>
+        <v>81</v>
       </c>
       <c r="M16">
-        <v>355</v>
+        <v>72</v>
       </c>
       <c r="N16">
-        <v>245</v>
+        <v>96</v>
       </c>
       <c r="O16">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="P16">
-        <v>285</v>
+        <v>89</v>
       </c>
       <c r="Q16">
-        <v>285</v>
+        <v>130</v>
       </c>
       <c r="R16">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="S16">
-        <v>715</v>
+        <v>150</v>
       </c>
       <c r="T16">
-        <v>415</v>
+        <v>72</v>
       </c>
       <c r="U16">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="V16">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="W16">
-        <v>295</v>
+        <v>70</v>
       </c>
       <c r="X16">
-        <v>335</v>
+        <v>90</v>
       </c>
       <c r="Y16">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="Z16">
-        <v>325</v>
+        <v>69</v>
       </c>
       <c r="AA16">
-        <v>265</v>
+        <v>69</v>
       </c>
       <c r="AB16">
-        <v>295</v>
+        <v>70</v>
       </c>
       <c r="AC16">
-        <v>315</v>
+        <v>69</v>
       </c>
       <c r="AD16">
-        <v>315</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
@@ -2474,88 +2601,88 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
-      </c>
-      <c r="C17" s="10">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D17">
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G17">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="H17">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="I17">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="J17">
-        <v>300</v>
+        <v>69</v>
       </c>
       <c r="K17">
-        <v>380</v>
+        <v>67</v>
       </c>
       <c r="L17">
-        <v>300</v>
+        <v>79</v>
       </c>
       <c r="M17">
-        <v>370</v>
+        <v>68</v>
       </c>
       <c r="N17">
-        <v>260</v>
+        <v>69</v>
       </c>
       <c r="O17">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="P17">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="Q17">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="R17">
-        <v>315</v>
+        <v>92</v>
       </c>
       <c r="S17">
-        <v>730</v>
+        <v>80</v>
       </c>
       <c r="T17">
-        <v>430</v>
+        <v>72</v>
       </c>
       <c r="U17">
-        <v>300</v>
+        <v>69</v>
       </c>
       <c r="V17">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="W17">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="X17">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="Y17">
-        <v>310</v>
+        <v>66</v>
       </c>
       <c r="Z17">
-        <v>340</v>
+        <v>69</v>
       </c>
       <c r="AA17">
-        <v>280</v>
+        <v>69</v>
       </c>
       <c r="AB17">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="AC17">
-        <v>330</v>
+        <v>69</v>
       </c>
       <c r="AD17">
-        <v>330</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
@@ -2563,88 +2690,88 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="10">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
+        <v>7</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D18">
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G18">
-        <v>595</v>
+        <v>115</v>
       </c>
       <c r="H18">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="I18">
-        <v>300</v>
+        <v>84</v>
       </c>
       <c r="J18">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="K18">
-        <v>400</v>
+        <v>90</v>
       </c>
       <c r="L18">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="M18">
-        <v>390</v>
+        <v>70</v>
       </c>
       <c r="N18">
-        <v>280</v>
+        <v>69</v>
       </c>
       <c r="O18">
-        <v>400</v>
+        <v>93</v>
       </c>
       <c r="P18">
-        <v>320</v>
+        <v>89</v>
       </c>
       <c r="Q18">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="R18">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="S18">
-        <v>750</v>
+        <v>78</v>
       </c>
       <c r="T18">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="U18">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="V18">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="W18">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="X18">
-        <v>370</v>
+        <v>90</v>
       </c>
       <c r="Y18">
-        <v>330</v>
+        <v>66</v>
       </c>
       <c r="Z18">
-        <v>360</v>
+        <v>69</v>
       </c>
       <c r="AA18">
-        <v>300</v>
+        <v>69</v>
       </c>
       <c r="AB18">
-        <v>330</v>
+        <v>68</v>
       </c>
       <c r="AC18">
-        <v>350</v>
+        <v>69</v>
       </c>
       <c r="AD18">
-        <v>350</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
@@ -2652,88 +2779,88 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6">
         <v>0.15</v>
       </c>
-      <c r="D19" t="s">
-        <v>35</v>
+      <c r="D19">
+        <v>17</v>
       </c>
       <c r="E19" t="s">
         <v>34</v>
       </c>
       <c r="G19">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H19">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I19">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J19">
         <v>69</v>
       </c>
       <c r="K19">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="L19">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M19">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N19">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="O19">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="P19">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="Q19">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="R19">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="S19">
         <v>76</v>
       </c>
       <c r="T19">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="U19">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="V19">
         <v>70</v>
       </c>
       <c r="W19">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X19">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Y19">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="Z19">
         <v>69</v>
       </c>
       <c r="AA19">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AB19">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC19">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AD19">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
@@ -2741,13 +2868,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6">
         <v>0.15</v>
       </c>
-      <c r="D20" t="s">
-        <v>35</v>
+      <c r="D20">
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>34</v>
@@ -2756,34 +2883,34 @@
         <v>76</v>
       </c>
       <c r="H20">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I20">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J20">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K20">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="L20">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="M20">
         <v>68</v>
       </c>
       <c r="N20">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="O20">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P20">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q20">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R20">
         <v>92</v>
@@ -2792,37 +2919,37 @@
         <v>76</v>
       </c>
       <c r="T20">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="U20">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="V20">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="W20">
         <v>68</v>
       </c>
       <c r="X20">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Y20">
         <v>66</v>
       </c>
       <c r="Z20">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA20">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AB20">
         <v>68</v>
       </c>
       <c r="AC20">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AD20">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
@@ -2830,19 +2957,19 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6">
         <v>0.15</v>
       </c>
       <c r="D21">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>34</v>
       </c>
       <c r="G21">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>70</v>
@@ -2854,13 +2981,13 @@
         <v>69</v>
       </c>
       <c r="K21">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L21">
         <v>79</v>
       </c>
       <c r="M21">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N21">
         <v>69</v>
@@ -2872,13 +2999,13 @@
         <v>89</v>
       </c>
       <c r="Q21">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="R21">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="S21">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="T21">
         <v>70</v>
@@ -2890,13 +3017,13 @@
         <v>70</v>
       </c>
       <c r="W21">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="X21">
         <v>90</v>
       </c>
       <c r="Y21">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Z21">
         <v>69</v>
@@ -2905,7 +3032,7 @@
         <v>69</v>
       </c>
       <c r="AB21">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC21">
         <v>69</v>
@@ -2919,88 +3046,85 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>189</v>
+        <v>7</v>
       </c>
       <c r="C22" s="6">
         <v>0.15</v>
       </c>
       <c r="D22">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G22">
-        <v>445</v>
+        <v>76</v>
       </c>
       <c r="H22">
-        <v>445</v>
+        <v>70</v>
       </c>
       <c r="I22">
-        <v>445</v>
+        <v>87</v>
       </c>
       <c r="J22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="K22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="L22">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="M22">
-        <v>445</v>
+        <v>68</v>
       </c>
       <c r="N22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="O22">
-        <v>445</v>
+        <v>90</v>
       </c>
       <c r="P22">
-        <v>445</v>
+        <v>89</v>
       </c>
       <c r="Q22">
-        <v>445</v>
+        <v>76</v>
       </c>
       <c r="R22">
-        <v>550</v>
+        <v>92</v>
       </c>
       <c r="S22">
-        <v>550</v>
+        <v>76</v>
       </c>
       <c r="T22">
-        <v>445</v>
+        <v>70</v>
       </c>
       <c r="U22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="V22">
-        <v>445</v>
+        <v>70</v>
       </c>
       <c r="W22">
-        <v>445</v>
+        <v>68</v>
       </c>
       <c r="X22">
-        <v>445</v>
+        <v>90</v>
       </c>
       <c r="Y22">
-        <v>445</v>
+        <v>66</v>
       </c>
       <c r="Z22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="AA22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="AB22">
-        <v>445</v>
+        <v>68</v>
       </c>
       <c r="AC22">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="AD22">
-        <v>445</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
@@ -3008,452 +3132,452 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.15</v>
+        <v>147</v>
+      </c>
+      <c r="C23" s="10">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="G23">
-        <v>165</v>
+        <v>595</v>
       </c>
       <c r="H23">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="I23">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="J23">
-        <v>165</v>
+        <v>320</v>
       </c>
       <c r="K23">
-        <v>190</v>
+        <v>400</v>
       </c>
       <c r="L23">
-        <v>165</v>
+        <v>320</v>
       </c>
       <c r="M23">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="N23">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="O23">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="P23">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="Q23">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="R23">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="S23">
-        <v>190</v>
+        <v>750</v>
       </c>
       <c r="T23">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="U23">
-        <v>165</v>
+        <v>320</v>
       </c>
       <c r="V23">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="W23">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="X23">
-        <v>165</v>
+        <v>370</v>
       </c>
       <c r="Y23">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="Z23">
-        <v>165</v>
+        <v>360</v>
       </c>
       <c r="AA23">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="AB23">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="AC23">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="AD23">
-        <v>165</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="D24" t="s">
-        <v>35</v>
+        <v>147</v>
+      </c>
+      <c r="C24" s="10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D24">
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="G24">
-        <v>200</v>
+        <v>720</v>
       </c>
       <c r="H24">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="I24">
-        <v>245</v>
+        <v>500</v>
       </c>
       <c r="J24">
-        <v>198</v>
+        <v>370</v>
       </c>
       <c r="K24">
-        <v>195</v>
+        <v>450</v>
       </c>
       <c r="L24">
-        <v>210</v>
+        <v>370</v>
       </c>
       <c r="M24">
-        <v>215</v>
+        <v>440</v>
       </c>
       <c r="N24">
-        <v>160</v>
+        <v>330</v>
       </c>
       <c r="O24">
-        <v>285</v>
+        <v>450</v>
       </c>
       <c r="P24">
-        <v>215</v>
+        <v>370</v>
       </c>
       <c r="Q24">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="R24">
-        <v>280</v>
+        <v>385</v>
       </c>
       <c r="S24">
-        <v>235</v>
+        <v>800</v>
       </c>
       <c r="T24">
-        <v>215</v>
+        <v>500</v>
       </c>
       <c r="U24">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="V24">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="W24">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="X24">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="Y24">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="Z24">
-        <v>160</v>
+        <v>410</v>
       </c>
       <c r="AA24">
-        <v>185</v>
+        <v>350</v>
       </c>
       <c r="AB24">
-        <v>200</v>
+        <v>380</v>
       </c>
       <c r="AC24">
-        <v>215</v>
+        <v>400</v>
       </c>
       <c r="AD24">
-        <v>185</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.1</v>
+        <v>147</v>
+      </c>
+      <c r="C25" s="10">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="G25">
-        <v>210</v>
+        <v>550</v>
       </c>
       <c r="H25">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="I25">
+        <v>415</v>
+      </c>
+      <c r="J25">
+        <v>385</v>
+      </c>
+      <c r="K25">
+        <v>365</v>
+      </c>
+      <c r="L25">
+        <v>285</v>
+      </c>
+      <c r="M25">
+        <v>355</v>
+      </c>
+      <c r="N25">
         <v>245</v>
       </c>
-      <c r="J25">
-        <v>198</v>
-      </c>
-      <c r="K25">
-        <v>195</v>
-      </c>
-      <c r="L25">
-        <v>210</v>
-      </c>
-      <c r="M25">
-        <v>215</v>
-      </c>
-      <c r="N25">
-        <v>170</v>
-      </c>
       <c r="O25">
+        <v>365</v>
+      </c>
+      <c r="P25">
         <v>285</v>
       </c>
-      <c r="P25">
-        <v>215</v>
-      </c>
       <c r="Q25">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="R25">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="S25">
-        <v>245</v>
+        <v>715</v>
       </c>
       <c r="T25">
-        <v>215</v>
+        <v>415</v>
       </c>
       <c r="U25">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="V25">
-        <v>220</v>
+        <v>315</v>
       </c>
       <c r="W25">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="X25">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="Y25">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="Z25">
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="AA25">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="AB25">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="AC25">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="AD25">
-        <v>185</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.1</v>
+        <v>183</v>
+      </c>
+      <c r="C26" s="10">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D26" t="s">
         <v>35</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="G26">
-        <v>205</v>
+        <v>550</v>
       </c>
       <c r="H26">
-        <v>235</v>
+        <v>330</v>
       </c>
       <c r="I26">
-        <v>265</v>
+        <v>430</v>
       </c>
       <c r="J26">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="K26">
-        <v>275</v>
+        <v>380</v>
       </c>
       <c r="L26">
-        <v>245</v>
+        <v>300</v>
       </c>
       <c r="M26">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="N26">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O26">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="P26">
-        <v>230</v>
+        <v>300</v>
       </c>
       <c r="Q26">
-        <v>162</v>
+        <v>300</v>
       </c>
       <c r="R26">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="S26">
-        <v>250</v>
+        <v>730</v>
       </c>
       <c r="T26">
-        <v>230</v>
+        <v>430</v>
       </c>
       <c r="U26">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="V26">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="W26">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="X26">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="Y26">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="Z26">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="AA26">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="AB26">
-        <v>220</v>
+        <v>310</v>
       </c>
       <c r="AC26">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="AD26">
-        <v>185</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.1</v>
+        <v>184</v>
+      </c>
+      <c r="C27" s="10">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D27" t="s">
         <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="G27">
-        <v>298</v>
+        <v>595</v>
       </c>
       <c r="H27">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="I27">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="J27">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="K27">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="L27">
+        <v>320</v>
+      </c>
+      <c r="M27">
+        <v>390</v>
+      </c>
+      <c r="N27">
         <v>280</v>
       </c>
-      <c r="M27">
-        <v>355</v>
-      </c>
-      <c r="N27">
+      <c r="O27">
+        <v>400</v>
+      </c>
+      <c r="P27">
+        <v>320</v>
+      </c>
+      <c r="Q27">
+        <v>320</v>
+      </c>
+      <c r="R27">
+        <v>335</v>
+      </c>
+      <c r="S27">
+        <v>750</v>
+      </c>
+      <c r="T27">
+        <v>450</v>
+      </c>
+      <c r="U27">
+        <v>320</v>
+      </c>
+      <c r="V27">
+        <v>350</v>
+      </c>
+      <c r="W27">
+        <v>330</v>
+      </c>
+      <c r="X27">
+        <v>370</v>
+      </c>
+      <c r="Y27">
+        <v>330</v>
+      </c>
+      <c r="Z27">
         <v>360</v>
       </c>
-      <c r="O27">
-        <v>440</v>
-      </c>
-      <c r="P27">
-        <v>355</v>
-      </c>
-      <c r="Q27">
-        <v>278</v>
-      </c>
-      <c r="R27">
-        <v>435</v>
-      </c>
-      <c r="S27">
-        <v>400</v>
-      </c>
-      <c r="T27">
-        <v>270</v>
-      </c>
-      <c r="U27">
-        <v>195</v>
-      </c>
-      <c r="V27">
-        <v>345</v>
-      </c>
-      <c r="W27">
-        <v>235</v>
-      </c>
-      <c r="X27">
-        <v>428</v>
-      </c>
-      <c r="Y27">
-        <v>270</v>
-      </c>
-      <c r="Z27">
-        <v>240</v>
-      </c>
       <c r="AA27">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="AB27">
-        <v>235</v>
+        <v>330</v>
       </c>
       <c r="AC27">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="AD27">
-        <v>288</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C28" s="6">
         <v>0.15</v>
@@ -3464,266 +3588,257 @@
       <c r="E28" t="s">
         <v>34</v>
       </c>
-      <c r="F28" t="s">
-        <v>60</v>
-      </c>
       <c r="G28">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="H28">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="I28">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="J28">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="K28">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="L28">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="M28">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="N28">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="O28">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="P28">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="Q28">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="R28">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="S28">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="T28">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="U28">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="V28">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="W28">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="X28">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="Y28">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="Z28">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="AA28">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AB28">
-        <v>167</v>
+        <v>70</v>
       </c>
       <c r="AC28">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AD28">
-        <v>167</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C29" s="6">
         <v>0.15</v>
       </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="s">
-        <v>34</v>
+      <c r="D29">
+        <v>23</v>
       </c>
       <c r="G29">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="H29">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="I29">
+        <v>84</v>
+      </c>
+      <c r="J29">
+        <v>69</v>
+      </c>
+      <c r="K29">
+        <v>71</v>
+      </c>
+      <c r="L29">
+        <v>83</v>
+      </c>
+      <c r="M29">
+        <v>73</v>
+      </c>
+      <c r="N29">
+        <v>76</v>
+      </c>
+      <c r="O29">
         <v>180</v>
       </c>
-      <c r="J29">
-        <v>165</v>
-      </c>
-      <c r="K29">
-        <v>190</v>
-      </c>
-      <c r="L29">
-        <v>165</v>
-      </c>
-      <c r="M29">
-        <v>170</v>
-      </c>
-      <c r="N29">
-        <v>165</v>
-      </c>
-      <c r="O29">
-        <v>165</v>
-      </c>
       <c r="P29">
-        <v>170</v>
+        <v>93</v>
       </c>
       <c r="Q29">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="R29">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="S29">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="T29">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="U29">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="V29">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="W29">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="X29">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="Y29">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="Z29">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="AA29">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AB29">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="AC29">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD29">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C30" s="6">
         <v>0.15</v>
       </c>
-      <c r="D30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" t="s">
-        <v>34</v>
+      <c r="D30">
+        <v>24</v>
       </c>
       <c r="G30">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="H30">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="I30">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="J30">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="K30">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="L30">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="M30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="N30">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="O30">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="P30">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="Q30">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="R30">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="S30">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="T30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="U30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="V30">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="W30">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="X30">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="Y30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="Z30">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="AA30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AB30">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="AC30">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AD30">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C31" s="6">
         <v>0.15</v>
@@ -3735,342 +3850,2270 @@
         <v>34</v>
       </c>
       <c r="G31">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="H31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="I31">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="J31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="K31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="L31">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="M31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="N31">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="O31">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="P31">
-        <v>218</v>
+        <v>87</v>
       </c>
       <c r="Q31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="R31">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="S31">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="T31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="U31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="V31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="W31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="X31">
-        <v>218</v>
+        <v>88</v>
       </c>
       <c r="Y31">
-        <v>218</v>
+        <v>66</v>
       </c>
       <c r="Z31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="AA31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="AB31">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="AC31">
-        <v>218</v>
+        <v>67</v>
       </c>
       <c r="AD31">
-        <v>218</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="10">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="D32" t="s">
-        <v>35</v>
+        <v>52</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="G32">
-        <v>740</v>
+        <v>105</v>
       </c>
       <c r="H32">
-        <v>400</v>
+        <v>68</v>
       </c>
       <c r="I32">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="J32">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="K32">
-        <v>450</v>
+        <v>69</v>
       </c>
       <c r="L32">
-        <v>370</v>
+        <v>79</v>
       </c>
       <c r="M32">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="N32">
-        <v>330</v>
+        <v>72</v>
       </c>
       <c r="O32">
-        <v>450</v>
+        <v>91</v>
       </c>
       <c r="P32">
-        <v>370</v>
+        <v>87</v>
       </c>
       <c r="Q32">
-        <v>370</v>
+        <v>95</v>
       </c>
       <c r="R32">
-        <v>385</v>
+        <v>95</v>
       </c>
       <c r="S32">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="T32">
-        <v>500</v>
+        <v>68</v>
       </c>
       <c r="U32">
-        <v>370</v>
+        <v>67</v>
       </c>
       <c r="V32">
-        <v>400</v>
+        <v>68</v>
       </c>
       <c r="W32">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="X32">
-        <v>420</v>
+        <v>88</v>
       </c>
       <c r="Y32">
-        <v>380</v>
+        <v>66</v>
       </c>
       <c r="Z32">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="AA32">
-        <v>350</v>
+        <v>67</v>
       </c>
       <c r="AB32">
-        <v>380</v>
+        <v>68</v>
       </c>
       <c r="AC32">
-        <v>400</v>
+        <v>67</v>
       </c>
       <c r="AD32">
-        <v>400</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C33" s="10">
-        <v>7.4999999999999997E-2</v>
+        <v>52</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.15</v>
       </c>
       <c r="D33">
-        <v>17</v>
-      </c>
-      <c r="E33" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="G33">
-        <v>780</v>
+        <v>78</v>
       </c>
       <c r="H33">
-        <v>440</v>
+        <v>68</v>
       </c>
       <c r="I33">
-        <v>540</v>
+        <v>84</v>
       </c>
       <c r="J33">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="K33">
-        <v>490</v>
+        <v>67</v>
       </c>
       <c r="L33">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="M33">
-        <v>480</v>
+        <v>68</v>
       </c>
       <c r="N33">
-        <v>370</v>
+        <v>70</v>
       </c>
       <c r="O33">
-        <v>490</v>
+        <v>88</v>
       </c>
       <c r="P33">
-        <v>410</v>
+        <v>90</v>
       </c>
       <c r="Q33">
-        <v>410</v>
+        <v>85</v>
       </c>
       <c r="R33">
-        <v>425</v>
+        <v>92</v>
       </c>
       <c r="S33">
-        <v>840</v>
+        <v>78</v>
       </c>
       <c r="T33">
-        <v>540</v>
+        <v>70</v>
       </c>
       <c r="U33">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="V33">
-        <v>440</v>
+        <v>68</v>
       </c>
       <c r="W33">
-        <v>420</v>
+        <v>68</v>
       </c>
       <c r="X33">
-        <v>460</v>
+        <v>88</v>
       </c>
       <c r="Y33">
-        <v>420</v>
+        <v>66</v>
       </c>
       <c r="Z33">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="AA33">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="AB33">
-        <v>420</v>
+        <v>68</v>
       </c>
       <c r="AC33">
-        <v>440</v>
+        <v>67</v>
       </c>
       <c r="AD33">
-        <v>440</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D34">
+        <v>27</v>
+      </c>
+      <c r="G34">
+        <v>78</v>
+      </c>
+      <c r="H34">
+        <v>68</v>
+      </c>
+      <c r="I34">
+        <v>82</v>
+      </c>
+      <c r="J34">
+        <v>67</v>
+      </c>
+      <c r="K34">
+        <v>69</v>
+      </c>
+      <c r="L34">
+        <v>77</v>
+      </c>
+      <c r="M34">
+        <v>68</v>
+      </c>
+      <c r="N34">
+        <v>70</v>
+      </c>
+      <c r="O34">
+        <v>88</v>
+      </c>
+      <c r="P34">
+        <v>87</v>
+      </c>
+      <c r="Q34">
+        <v>68</v>
+      </c>
+      <c r="R34">
+        <v>92</v>
+      </c>
+      <c r="S34">
+        <v>76</v>
+      </c>
+      <c r="T34">
+        <v>68</v>
+      </c>
+      <c r="U34">
+        <v>67</v>
+      </c>
+      <c r="V34">
+        <v>68</v>
+      </c>
+      <c r="W34">
+        <v>68</v>
+      </c>
+      <c r="X34">
+        <v>88</v>
+      </c>
+      <c r="Y34">
+        <v>66</v>
+      </c>
+      <c r="Z34">
+        <v>67</v>
+      </c>
+      <c r="AA34">
+        <v>67</v>
+      </c>
+      <c r="AB34">
+        <v>68</v>
+      </c>
+      <c r="AC34">
+        <v>67</v>
+      </c>
+      <c r="AD34">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D35">
+        <v>28</v>
+      </c>
+      <c r="G35">
+        <v>78</v>
+      </c>
+      <c r="H35">
+        <v>68</v>
+      </c>
+      <c r="I35">
+        <v>82</v>
+      </c>
+      <c r="J35">
+        <v>67</v>
+      </c>
+      <c r="K35">
+        <v>67</v>
+      </c>
+      <c r="L35">
+        <v>77</v>
+      </c>
+      <c r="M35">
+        <v>68</v>
+      </c>
+      <c r="N35">
+        <v>72</v>
+      </c>
+      <c r="O35">
+        <v>88</v>
+      </c>
+      <c r="P35">
+        <v>87</v>
+      </c>
+      <c r="Q35">
+        <v>68</v>
+      </c>
+      <c r="R35">
+        <v>92</v>
+      </c>
+      <c r="S35">
+        <v>76</v>
+      </c>
+      <c r="T35">
+        <v>68</v>
+      </c>
+      <c r="U35">
+        <v>67</v>
+      </c>
+      <c r="V35">
+        <v>68</v>
+      </c>
+      <c r="W35">
+        <v>68</v>
+      </c>
+      <c r="X35">
+        <v>88</v>
+      </c>
+      <c r="Y35">
+        <v>66</v>
+      </c>
+      <c r="Z35">
+        <v>67</v>
+      </c>
+      <c r="AA35">
+        <v>67</v>
+      </c>
+      <c r="AB35">
+        <v>68</v>
+      </c>
+      <c r="AC35">
+        <v>67</v>
+      </c>
+      <c r="AD35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D36">
+        <v>29</v>
+      </c>
+      <c r="G36">
+        <v>190</v>
+      </c>
+      <c r="H36">
+        <v>68</v>
+      </c>
+      <c r="I36">
+        <v>82</v>
+      </c>
+      <c r="J36">
+        <v>67</v>
+      </c>
+      <c r="K36">
+        <v>67</v>
+      </c>
+      <c r="L36">
+        <v>77</v>
+      </c>
+      <c r="M36">
+        <v>68</v>
+      </c>
+      <c r="N36">
+        <v>70</v>
+      </c>
+      <c r="O36">
+        <v>88</v>
+      </c>
+      <c r="P36">
+        <v>87</v>
+      </c>
+      <c r="Q36">
+        <v>68</v>
+      </c>
+      <c r="R36">
+        <v>92</v>
+      </c>
+      <c r="S36">
+        <v>76</v>
+      </c>
+      <c r="T36">
+        <v>68</v>
+      </c>
+      <c r="U36">
+        <v>67</v>
+      </c>
+      <c r="V36">
+        <v>68</v>
+      </c>
+      <c r="W36">
+        <v>68</v>
+      </c>
+      <c r="X36">
+        <v>88</v>
+      </c>
+      <c r="Y36">
+        <v>68</v>
+      </c>
+      <c r="Z36">
+        <v>67</v>
+      </c>
+      <c r="AA36">
+        <v>67</v>
+      </c>
+      <c r="AB36">
+        <v>68</v>
+      </c>
+      <c r="AC36">
+        <v>67</v>
+      </c>
+      <c r="AD36">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="G37">
+        <v>78</v>
+      </c>
+      <c r="H37">
+        <v>68</v>
+      </c>
+      <c r="I37">
+        <v>82</v>
+      </c>
+      <c r="J37">
+        <v>67</v>
+      </c>
+      <c r="K37">
+        <v>67</v>
+      </c>
+      <c r="L37">
+        <v>77</v>
+      </c>
+      <c r="M37">
+        <v>68</v>
+      </c>
+      <c r="N37">
+        <v>70</v>
+      </c>
+      <c r="O37">
+        <v>88</v>
+      </c>
+      <c r="P37">
+        <v>87</v>
+      </c>
+      <c r="Q37">
+        <v>68</v>
+      </c>
+      <c r="R37">
+        <v>92</v>
+      </c>
+      <c r="S37">
+        <v>76</v>
+      </c>
+      <c r="T37">
+        <v>68</v>
+      </c>
+      <c r="U37">
+        <v>67</v>
+      </c>
+      <c r="V37">
+        <v>68</v>
+      </c>
+      <c r="W37">
+        <v>68</v>
+      </c>
+      <c r="X37">
+        <v>88</v>
+      </c>
+      <c r="Y37">
+        <v>66</v>
+      </c>
+      <c r="Z37">
+        <v>67</v>
+      </c>
+      <c r="AA37">
+        <v>67</v>
+      </c>
+      <c r="AB37">
+        <v>68</v>
+      </c>
+      <c r="AC37">
+        <v>67</v>
+      </c>
+      <c r="AD37">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D38">
+        <v>31</v>
+      </c>
+      <c r="G38">
+        <v>82</v>
+      </c>
+      <c r="H38">
+        <v>68</v>
+      </c>
+      <c r="I38">
+        <v>82</v>
+      </c>
+      <c r="J38">
+        <v>67</v>
+      </c>
+      <c r="K38">
+        <v>69</v>
+      </c>
+      <c r="L38">
+        <v>77</v>
+      </c>
+      <c r="M38">
+        <v>68</v>
+      </c>
+      <c r="N38">
+        <v>72</v>
+      </c>
+      <c r="O38">
+        <v>88</v>
+      </c>
+      <c r="P38">
+        <v>87</v>
+      </c>
+      <c r="Q38">
+        <v>68</v>
+      </c>
+      <c r="R38">
+        <v>92</v>
+      </c>
+      <c r="S38">
+        <v>76</v>
+      </c>
+      <c r="T38">
+        <v>68</v>
+      </c>
+      <c r="U38">
+        <v>67</v>
+      </c>
+      <c r="V38">
+        <v>68</v>
+      </c>
+      <c r="W38">
+        <v>68</v>
+      </c>
+      <c r="X38">
+        <v>88</v>
+      </c>
+      <c r="Y38">
+        <v>66</v>
+      </c>
+      <c r="Z38">
+        <v>67</v>
+      </c>
+      <c r="AA38">
+        <v>67</v>
+      </c>
+      <c r="AB38">
+        <v>68</v>
+      </c>
+      <c r="AC38">
+        <v>67</v>
+      </c>
+      <c r="AD38">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D39">
+        <v>32</v>
+      </c>
+      <c r="G39">
+        <v>78</v>
+      </c>
+      <c r="H39">
+        <v>68</v>
+      </c>
+      <c r="I39">
+        <v>82</v>
+      </c>
+      <c r="J39">
+        <v>67</v>
+      </c>
+      <c r="K39">
+        <v>69</v>
+      </c>
+      <c r="L39">
+        <v>77</v>
+      </c>
+      <c r="M39">
+        <v>68</v>
+      </c>
+      <c r="N39">
+        <v>70</v>
+      </c>
+      <c r="O39">
+        <v>88</v>
+      </c>
+      <c r="P39">
+        <v>87</v>
+      </c>
+      <c r="Q39">
+        <v>68</v>
+      </c>
+      <c r="R39">
+        <v>92</v>
+      </c>
+      <c r="S39">
+        <v>76</v>
+      </c>
+      <c r="T39">
+        <v>68</v>
+      </c>
+      <c r="U39">
+        <v>67</v>
+      </c>
+      <c r="V39">
+        <v>68</v>
+      </c>
+      <c r="W39">
+        <v>68</v>
+      </c>
+      <c r="X39">
+        <v>88</v>
+      </c>
+      <c r="Y39">
+        <v>66</v>
+      </c>
+      <c r="Z39">
+        <v>67</v>
+      </c>
+      <c r="AA39">
+        <v>67</v>
+      </c>
+      <c r="AB39">
+        <v>68</v>
+      </c>
+      <c r="AC39">
+        <v>67</v>
+      </c>
+      <c r="AD39">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D40">
+        <v>33</v>
+      </c>
+      <c r="G40">
+        <v>78</v>
+      </c>
+      <c r="H40">
+        <v>68</v>
+      </c>
+      <c r="I40">
+        <v>82</v>
+      </c>
+      <c r="J40">
+        <v>67</v>
+      </c>
+      <c r="K40">
+        <v>71</v>
+      </c>
+      <c r="L40">
+        <v>77</v>
+      </c>
+      <c r="M40">
+        <v>68</v>
+      </c>
+      <c r="N40">
+        <v>70</v>
+      </c>
+      <c r="O40">
+        <v>88</v>
+      </c>
+      <c r="P40">
+        <v>87</v>
+      </c>
+      <c r="Q40">
+        <v>90</v>
+      </c>
+      <c r="R40">
+        <v>92</v>
+      </c>
+      <c r="S40">
+        <v>76</v>
+      </c>
+      <c r="T40">
+        <v>68</v>
+      </c>
+      <c r="U40">
+        <v>67</v>
+      </c>
+      <c r="V40">
+        <v>68</v>
+      </c>
+      <c r="W40">
+        <v>68</v>
+      </c>
+      <c r="X40">
+        <v>88</v>
+      </c>
+      <c r="Y40">
+        <v>68</v>
+      </c>
+      <c r="Z40">
+        <v>67</v>
+      </c>
+      <c r="AA40">
+        <v>67</v>
+      </c>
+      <c r="AB40">
+        <v>68</v>
+      </c>
+      <c r="AC40">
+        <v>67</v>
+      </c>
+      <c r="AD40">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D41">
+        <v>34</v>
+      </c>
+      <c r="G41">
+        <v>78</v>
+      </c>
+      <c r="H41">
+        <v>68</v>
+      </c>
+      <c r="I41">
+        <v>82</v>
+      </c>
+      <c r="J41">
+        <v>67</v>
+      </c>
+      <c r="K41">
+        <v>72</v>
+      </c>
+      <c r="L41">
+        <v>77</v>
+      </c>
+      <c r="M41">
+        <v>68</v>
+      </c>
+      <c r="N41">
+        <v>72</v>
+      </c>
+      <c r="O41">
+        <v>88</v>
+      </c>
+      <c r="P41">
+        <v>87</v>
+      </c>
+      <c r="Q41">
+        <v>95</v>
+      </c>
+      <c r="R41">
+        <v>95</v>
+      </c>
+      <c r="S41">
+        <v>76</v>
+      </c>
+      <c r="T41">
+        <v>68</v>
+      </c>
+      <c r="U41">
+        <v>67</v>
+      </c>
+      <c r="V41">
+        <v>68</v>
+      </c>
+      <c r="W41">
+        <v>68</v>
+      </c>
+      <c r="X41">
+        <v>88</v>
+      </c>
+      <c r="Y41">
+        <v>66</v>
+      </c>
+      <c r="Z41">
+        <v>67</v>
+      </c>
+      <c r="AA41">
+        <v>67</v>
+      </c>
+      <c r="AB41">
+        <v>68</v>
+      </c>
+      <c r="AC41">
+        <v>67</v>
+      </c>
+      <c r="AD41">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D42">
+        <v>35</v>
+      </c>
+      <c r="G42">
+        <v>78</v>
+      </c>
+      <c r="H42">
+        <v>68</v>
+      </c>
+      <c r="I42">
+        <v>82</v>
+      </c>
+      <c r="J42">
+        <v>67</v>
+      </c>
+      <c r="K42">
+        <v>67</v>
+      </c>
+      <c r="L42">
+        <v>77</v>
+      </c>
+      <c r="M42">
+        <v>68</v>
+      </c>
+      <c r="N42">
+        <v>72</v>
+      </c>
+      <c r="O42">
+        <v>88</v>
+      </c>
+      <c r="P42">
+        <v>87</v>
+      </c>
+      <c r="Q42">
+        <v>68</v>
+      </c>
+      <c r="R42">
+        <v>92</v>
+      </c>
+      <c r="S42">
+        <v>76</v>
+      </c>
+      <c r="T42">
+        <v>68</v>
+      </c>
+      <c r="U42">
+        <v>67</v>
+      </c>
+      <c r="V42">
+        <v>68</v>
+      </c>
+      <c r="W42">
+        <v>68</v>
+      </c>
+      <c r="X42">
+        <v>88</v>
+      </c>
+      <c r="Y42">
+        <v>66</v>
+      </c>
+      <c r="Z42">
+        <v>69</v>
+      </c>
+      <c r="AA42">
+        <v>67</v>
+      </c>
+      <c r="AB42">
+        <v>68</v>
+      </c>
+      <c r="AC42">
+        <v>67</v>
+      </c>
+      <c r="AD42">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D43">
+        <v>36</v>
+      </c>
+      <c r="G43">
+        <v>78</v>
+      </c>
+      <c r="H43">
+        <v>68</v>
+      </c>
+      <c r="I43">
+        <v>82</v>
+      </c>
+      <c r="J43">
+        <v>67</v>
+      </c>
+      <c r="K43">
+        <v>67</v>
+      </c>
+      <c r="L43">
+        <v>77</v>
+      </c>
+      <c r="M43">
+        <v>68</v>
+      </c>
+      <c r="N43">
+        <v>72</v>
+      </c>
+      <c r="O43">
+        <v>88</v>
+      </c>
+      <c r="P43">
+        <v>87</v>
+      </c>
+      <c r="Q43">
+        <v>68</v>
+      </c>
+      <c r="R43">
+        <v>92</v>
+      </c>
+      <c r="S43">
+        <v>78</v>
+      </c>
+      <c r="T43">
+        <v>70</v>
+      </c>
+      <c r="U43">
+        <v>67</v>
+      </c>
+      <c r="V43">
+        <v>68</v>
+      </c>
+      <c r="W43">
+        <v>68</v>
+      </c>
+      <c r="X43">
+        <v>88</v>
+      </c>
+      <c r="Y43">
+        <v>66</v>
+      </c>
+      <c r="Z43">
+        <v>67</v>
+      </c>
+      <c r="AA43">
+        <v>67</v>
+      </c>
+      <c r="AB43">
+        <v>68</v>
+      </c>
+      <c r="AC43">
+        <v>67</v>
+      </c>
+      <c r="AD43">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
         <v>186</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C44" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D44">
+        <v>37</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44">
+        <v>445</v>
+      </c>
+      <c r="H44">
+        <v>445</v>
+      </c>
+      <c r="I44">
+        <v>445</v>
+      </c>
+      <c r="J44">
+        <v>445</v>
+      </c>
+      <c r="K44">
+        <v>445</v>
+      </c>
+      <c r="L44">
+        <v>445</v>
+      </c>
+      <c r="M44">
+        <v>445</v>
+      </c>
+      <c r="N44">
+        <v>445</v>
+      </c>
+      <c r="O44">
+        <v>445</v>
+      </c>
+      <c r="P44">
+        <v>445</v>
+      </c>
+      <c r="Q44">
+        <v>445</v>
+      </c>
+      <c r="R44">
+        <v>550</v>
+      </c>
+      <c r="S44">
+        <v>550</v>
+      </c>
+      <c r="T44">
+        <v>445</v>
+      </c>
+      <c r="U44">
+        <v>445</v>
+      </c>
+      <c r="V44">
+        <v>445</v>
+      </c>
+      <c r="W44">
+        <v>445</v>
+      </c>
+      <c r="X44">
+        <v>445</v>
+      </c>
+      <c r="Y44">
+        <v>445</v>
+      </c>
+      <c r="Z44">
+        <v>445</v>
+      </c>
+      <c r="AA44">
+        <v>445</v>
+      </c>
+      <c r="AB44">
+        <v>445</v>
+      </c>
+      <c r="AC44">
+        <v>445</v>
+      </c>
+      <c r="AD44">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" t="s">
+        <v>34</v>
+      </c>
+      <c r="G45">
+        <v>165</v>
+      </c>
+      <c r="H45">
+        <v>165</v>
+      </c>
+      <c r="I45">
+        <v>180</v>
+      </c>
+      <c r="J45">
+        <v>165</v>
+      </c>
+      <c r="K45">
+        <v>190</v>
+      </c>
+      <c r="L45">
+        <v>165</v>
+      </c>
+      <c r="M45">
+        <v>170</v>
+      </c>
+      <c r="N45">
+        <v>165</v>
+      </c>
+      <c r="O45">
+        <v>165</v>
+      </c>
+      <c r="P45">
+        <v>170</v>
+      </c>
+      <c r="Q45">
+        <v>170</v>
+      </c>
+      <c r="R45">
+        <v>170</v>
+      </c>
+      <c r="S45">
+        <v>190</v>
+      </c>
+      <c r="T45">
+        <v>165</v>
+      </c>
+      <c r="U45">
+        <v>165</v>
+      </c>
+      <c r="V45">
+        <v>165</v>
+      </c>
+      <c r="W45">
+        <v>165</v>
+      </c>
+      <c r="X45">
+        <v>165</v>
+      </c>
+      <c r="Y45">
+        <v>170</v>
+      </c>
+      <c r="Z45">
+        <v>165</v>
+      </c>
+      <c r="AA45">
+        <v>165</v>
+      </c>
+      <c r="AB45">
+        <v>165</v>
+      </c>
+      <c r="AC45">
+        <v>165</v>
+      </c>
+      <c r="AD45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46">
+        <v>225</v>
+      </c>
+      <c r="I46">
+        <v>245</v>
+      </c>
+      <c r="J46">
+        <v>198</v>
+      </c>
+      <c r="K46">
+        <v>195</v>
+      </c>
+      <c r="L46">
+        <v>210</v>
+      </c>
+      <c r="M46">
+        <v>215</v>
+      </c>
+      <c r="N46">
+        <v>160</v>
+      </c>
+      <c r="O46">
+        <v>285</v>
+      </c>
+      <c r="P46">
+        <v>215</v>
+      </c>
+      <c r="Q46">
+        <v>160</v>
+      </c>
+      <c r="R46">
+        <v>280</v>
+      </c>
+      <c r="S46">
+        <v>235</v>
+      </c>
+      <c r="T46">
+        <v>215</v>
+      </c>
+      <c r="U46">
+        <v>200</v>
+      </c>
+      <c r="V46">
+        <v>220</v>
+      </c>
+      <c r="W46">
+        <v>200</v>
+      </c>
+      <c r="X46">
+        <v>278</v>
+      </c>
+      <c r="Y46">
+        <v>210</v>
+      </c>
+      <c r="Z46">
+        <v>160</v>
+      </c>
+      <c r="AA46">
+        <v>185</v>
+      </c>
+      <c r="AB46">
+        <v>200</v>
+      </c>
+      <c r="AC46">
+        <v>215</v>
+      </c>
+      <c r="AD46">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D47">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47">
+        <v>210</v>
+      </c>
+      <c r="H47">
+        <v>225</v>
+      </c>
+      <c r="I47">
+        <v>245</v>
+      </c>
+      <c r="J47">
+        <v>198</v>
+      </c>
+      <c r="K47">
+        <v>195</v>
+      </c>
+      <c r="L47">
+        <v>210</v>
+      </c>
+      <c r="M47">
+        <v>215</v>
+      </c>
+      <c r="N47">
+        <v>170</v>
+      </c>
+      <c r="O47">
+        <v>285</v>
+      </c>
+      <c r="P47">
+        <v>215</v>
+      </c>
+      <c r="Q47">
+        <v>165</v>
+      </c>
+      <c r="R47">
+        <v>280</v>
+      </c>
+      <c r="S47">
+        <v>245</v>
+      </c>
+      <c r="T47">
+        <v>215</v>
+      </c>
+      <c r="U47">
+        <v>200</v>
+      </c>
+      <c r="V47">
+        <v>220</v>
+      </c>
+      <c r="W47">
+        <v>200</v>
+      </c>
+      <c r="X47">
+        <v>278</v>
+      </c>
+      <c r="Y47">
+        <v>210</v>
+      </c>
+      <c r="Z47">
+        <v>160</v>
+      </c>
+      <c r="AA47">
+        <v>185</v>
+      </c>
+      <c r="AB47">
+        <v>200</v>
+      </c>
+      <c r="AC47">
+        <v>215</v>
+      </c>
+      <c r="AD47">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48">
+        <v>205</v>
+      </c>
+      <c r="H48">
+        <v>235</v>
+      </c>
+      <c r="I48">
+        <v>265</v>
+      </c>
+      <c r="J48">
+        <v>270</v>
+      </c>
+      <c r="K48">
+        <v>275</v>
+      </c>
+      <c r="L48">
+        <v>245</v>
+      </c>
+      <c r="M48">
+        <v>225</v>
+      </c>
+      <c r="N48">
+        <v>270</v>
+      </c>
+      <c r="O48">
+        <v>395</v>
+      </c>
+      <c r="P48">
+        <v>230</v>
+      </c>
+      <c r="Q48">
+        <v>162</v>
+      </c>
+      <c r="R48">
+        <v>370</v>
+      </c>
+      <c r="S48">
+        <v>250</v>
+      </c>
+      <c r="T48">
+        <v>230</v>
+      </c>
+      <c r="U48">
+        <v>185</v>
+      </c>
+      <c r="V48">
+        <v>328</v>
+      </c>
+      <c r="W48">
+        <v>220</v>
+      </c>
+      <c r="X48">
+        <v>400</v>
+      </c>
+      <c r="Y48">
+        <v>220</v>
+      </c>
+      <c r="Z48">
+        <v>210</v>
+      </c>
+      <c r="AA48">
+        <v>185</v>
+      </c>
+      <c r="AB48">
+        <v>220</v>
+      </c>
+      <c r="AC48">
+        <v>220</v>
+      </c>
+      <c r="AD48">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49">
+        <v>298</v>
+      </c>
+      <c r="H49">
+        <v>365</v>
+      </c>
+      <c r="I49">
+        <v>292</v>
+      </c>
+      <c r="J49">
+        <v>345</v>
+      </c>
+      <c r="K49">
+        <v>345</v>
+      </c>
+      <c r="L49">
+        <v>280</v>
+      </c>
+      <c r="M49">
+        <v>355</v>
+      </c>
+      <c r="N49">
+        <v>360</v>
+      </c>
+      <c r="O49">
+        <v>440</v>
+      </c>
+      <c r="P49">
+        <v>355</v>
+      </c>
+      <c r="Q49">
+        <v>278</v>
+      </c>
+      <c r="R49">
+        <v>435</v>
+      </c>
+      <c r="S49">
+        <v>400</v>
+      </c>
+      <c r="T49">
+        <v>270</v>
+      </c>
+      <c r="U49">
+        <v>195</v>
+      </c>
+      <c r="V49">
+        <v>345</v>
+      </c>
+      <c r="W49">
+        <v>235</v>
+      </c>
+      <c r="X49">
+        <v>428</v>
+      </c>
+      <c r="Y49">
+        <v>270</v>
+      </c>
+      <c r="Z49">
+        <v>240</v>
+      </c>
+      <c r="AA49">
+        <v>288</v>
+      </c>
+      <c r="AB49">
+        <v>235</v>
+      </c>
+      <c r="AC49">
+        <v>270</v>
+      </c>
+      <c r="AD49">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50">
+        <v>167</v>
+      </c>
+      <c r="H50">
+        <v>167</v>
+      </c>
+      <c r="I50">
+        <v>170</v>
+      </c>
+      <c r="J50">
+        <v>167</v>
+      </c>
+      <c r="K50">
+        <v>170</v>
+      </c>
+      <c r="L50">
+        <v>167</v>
+      </c>
+      <c r="M50">
+        <v>167</v>
+      </c>
+      <c r="N50">
+        <v>170</v>
+      </c>
+      <c r="O50">
+        <v>167</v>
+      </c>
+      <c r="P50">
+        <v>167</v>
+      </c>
+      <c r="Q50">
+        <v>170</v>
+      </c>
+      <c r="R50">
+        <v>170</v>
+      </c>
+      <c r="S50">
+        <v>170</v>
+      </c>
+      <c r="T50">
+        <v>167</v>
+      </c>
+      <c r="U50">
+        <v>167</v>
+      </c>
+      <c r="V50">
+        <v>167</v>
+      </c>
+      <c r="W50">
+        <v>167</v>
+      </c>
+      <c r="X50">
+        <v>167</v>
+      </c>
+      <c r="Y50">
+        <v>170</v>
+      </c>
+      <c r="Z50">
+        <v>167</v>
+      </c>
+      <c r="AA50">
+        <v>167</v>
+      </c>
+      <c r="AB50">
+        <v>167</v>
+      </c>
+      <c r="AC50">
+        <v>167</v>
+      </c>
+      <c r="AD50">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C51" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51">
+        <v>165</v>
+      </c>
+      <c r="H51">
+        <v>165</v>
+      </c>
+      <c r="I51">
+        <v>180</v>
+      </c>
+      <c r="J51">
+        <v>165</v>
+      </c>
+      <c r="K51">
+        <v>190</v>
+      </c>
+      <c r="L51">
+        <v>165</v>
+      </c>
+      <c r="M51">
+        <v>170</v>
+      </c>
+      <c r="N51">
+        <v>165</v>
+      </c>
+      <c r="O51">
+        <v>165</v>
+      </c>
+      <c r="P51">
+        <v>170</v>
+      </c>
+      <c r="Q51">
+        <v>170</v>
+      </c>
+      <c r="R51">
+        <v>170</v>
+      </c>
+      <c r="S51">
+        <v>190</v>
+      </c>
+      <c r="T51">
+        <v>165</v>
+      </c>
+      <c r="U51">
+        <v>165</v>
+      </c>
+      <c r="V51">
+        <v>165</v>
+      </c>
+      <c r="W51">
+        <v>165</v>
+      </c>
+      <c r="X51">
+        <v>165</v>
+      </c>
+      <c r="Y51">
+        <v>170</v>
+      </c>
+      <c r="Z51">
+        <v>165</v>
+      </c>
+      <c r="AA51">
+        <v>165</v>
+      </c>
+      <c r="AB51">
+        <v>165</v>
+      </c>
+      <c r="AC51">
+        <v>165</v>
+      </c>
+      <c r="AD51">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52">
+        <v>155</v>
+      </c>
+      <c r="H52">
+        <v>155</v>
+      </c>
+      <c r="I52">
+        <v>155</v>
+      </c>
+      <c r="J52">
+        <v>155</v>
+      </c>
+      <c r="K52">
+        <v>155</v>
+      </c>
+      <c r="L52">
+        <v>155</v>
+      </c>
+      <c r="M52">
+        <v>155</v>
+      </c>
+      <c r="N52">
+        <v>155</v>
+      </c>
+      <c r="O52">
+        <v>155</v>
+      </c>
+      <c r="P52">
+        <v>155</v>
+      </c>
+      <c r="Q52">
+        <v>155</v>
+      </c>
+      <c r="R52">
+        <v>155</v>
+      </c>
+      <c r="S52">
+        <v>155</v>
+      </c>
+      <c r="T52">
+        <v>155</v>
+      </c>
+      <c r="U52">
+        <v>155</v>
+      </c>
+      <c r="V52">
+        <v>155</v>
+      </c>
+      <c r="W52">
+        <v>155</v>
+      </c>
+      <c r="X52">
+        <v>155</v>
+      </c>
+      <c r="Y52">
+        <v>155</v>
+      </c>
+      <c r="Z52">
+        <v>155</v>
+      </c>
+      <c r="AA52">
+        <v>155</v>
+      </c>
+      <c r="AB52">
+        <v>155</v>
+      </c>
+      <c r="AC52">
+        <v>155</v>
+      </c>
+      <c r="AD52">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C53" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53">
+        <v>220</v>
+      </c>
+      <c r="H53">
+        <v>218</v>
+      </c>
+      <c r="I53">
+        <v>218</v>
+      </c>
+      <c r="J53">
+        <v>218</v>
+      </c>
+      <c r="K53">
+        <v>218</v>
+      </c>
+      <c r="L53">
+        <v>218</v>
+      </c>
+      <c r="M53">
+        <v>218</v>
+      </c>
+      <c r="N53">
+        <v>218</v>
+      </c>
+      <c r="O53">
+        <v>218</v>
+      </c>
+      <c r="P53">
+        <v>218</v>
+      </c>
+      <c r="Q53">
+        <v>218</v>
+      </c>
+      <c r="R53">
+        <v>218</v>
+      </c>
+      <c r="S53">
+        <v>218</v>
+      </c>
+      <c r="T53">
+        <v>218</v>
+      </c>
+      <c r="U53">
+        <v>218</v>
+      </c>
+      <c r="V53">
+        <v>218</v>
+      </c>
+      <c r="W53">
+        <v>218</v>
+      </c>
+      <c r="X53">
+        <v>218</v>
+      </c>
+      <c r="Y53">
+        <v>218</v>
+      </c>
+      <c r="Z53">
+        <v>218</v>
+      </c>
+      <c r="AA53">
+        <v>218</v>
+      </c>
+      <c r="AB53">
+        <v>218</v>
+      </c>
+      <c r="AC53">
+        <v>218</v>
+      </c>
+      <c r="AD53">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="10">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="D34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="s">
-        <v>149</v>
-      </c>
-      <c r="G34">
+      <c r="D54" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54">
+        <v>740</v>
+      </c>
+      <c r="H54">
+        <v>400</v>
+      </c>
+      <c r="I54">
+        <v>500</v>
+      </c>
+      <c r="J54">
+        <v>370</v>
+      </c>
+      <c r="K54">
+        <v>450</v>
+      </c>
+      <c r="L54">
+        <v>370</v>
+      </c>
+      <c r="M54">
+        <v>440</v>
+      </c>
+      <c r="N54">
+        <v>330</v>
+      </c>
+      <c r="O54">
+        <v>450</v>
+      </c>
+      <c r="P54">
+        <v>370</v>
+      </c>
+      <c r="Q54">
+        <v>370</v>
+      </c>
+      <c r="R54">
+        <v>385</v>
+      </c>
+      <c r="S54">
+        <v>800</v>
+      </c>
+      <c r="T54">
+        <v>500</v>
+      </c>
+      <c r="U54">
+        <v>370</v>
+      </c>
+      <c r="V54">
+        <v>400</v>
+      </c>
+      <c r="W54">
+        <v>380</v>
+      </c>
+      <c r="X54">
+        <v>420</v>
+      </c>
+      <c r="Y54">
+        <v>380</v>
+      </c>
+      <c r="Z54">
+        <v>410</v>
+      </c>
+      <c r="AA54">
+        <v>350</v>
+      </c>
+      <c r="AB54">
+        <v>380</v>
+      </c>
+      <c r="AC54">
+        <v>400</v>
+      </c>
+      <c r="AD54">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D55">
+        <v>39</v>
+      </c>
+      <c r="E55" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55">
+        <v>780</v>
+      </c>
+      <c r="H55">
+        <v>440</v>
+      </c>
+      <c r="I55">
+        <v>540</v>
+      </c>
+      <c r="J55">
+        <v>410</v>
+      </c>
+      <c r="K55">
+        <v>490</v>
+      </c>
+      <c r="L55">
+        <v>410</v>
+      </c>
+      <c r="M55">
+        <v>480</v>
+      </c>
+      <c r="N55">
+        <v>370</v>
+      </c>
+      <c r="O55">
+        <v>490</v>
+      </c>
+      <c r="P55">
+        <v>410</v>
+      </c>
+      <c r="Q55">
+        <v>410</v>
+      </c>
+      <c r="R55">
+        <v>425</v>
+      </c>
+      <c r="S55">
+        <v>840</v>
+      </c>
+      <c r="T55">
+        <v>540</v>
+      </c>
+      <c r="U55">
+        <v>410</v>
+      </c>
+      <c r="V55">
+        <v>440</v>
+      </c>
+      <c r="W55">
+        <v>420</v>
+      </c>
+      <c r="X55">
+        <v>460</v>
+      </c>
+      <c r="Y55">
+        <v>420</v>
+      </c>
+      <c r="Z55">
+        <v>450</v>
+      </c>
+      <c r="AA55">
+        <v>390</v>
+      </c>
+      <c r="AB55">
+        <v>420</v>
+      </c>
+      <c r="AC55">
+        <v>440</v>
+      </c>
+      <c r="AD55">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" s="10">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="D56" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" t="s">
+        <v>148</v>
+      </c>
+      <c r="G56">
         <v>580</v>
       </c>
-      <c r="H34">
+      <c r="H56">
         <v>360</v>
       </c>
-      <c r="I34">
+      <c r="I56">
         <v>460</v>
       </c>
-      <c r="J34">
+      <c r="J56">
         <v>330</v>
       </c>
-      <c r="K34">
+      <c r="K56">
         <v>410</v>
       </c>
-      <c r="L34">
+      <c r="L56">
         <v>330</v>
       </c>
-      <c r="M34">
+      <c r="M56">
         <v>400</v>
       </c>
-      <c r="N34">
+      <c r="N56">
         <v>290</v>
       </c>
-      <c r="O34">
+      <c r="O56">
         <v>410</v>
       </c>
-      <c r="P34">
+      <c r="P56">
         <v>330</v>
       </c>
-      <c r="Q34">
+      <c r="Q56">
         <v>330</v>
       </c>
-      <c r="R34">
+      <c r="R56">
         <v>345</v>
       </c>
-      <c r="S34">
+      <c r="S56">
         <v>760</v>
       </c>
-      <c r="T34">
+      <c r="T56">
         <v>460</v>
       </c>
-      <c r="U34">
+      <c r="U56">
         <v>330</v>
       </c>
-      <c r="V34">
+      <c r="V56">
         <v>360</v>
       </c>
-      <c r="W34">
+      <c r="W56">
         <v>340</v>
       </c>
-      <c r="X34">
+      <c r="X56">
         <v>380</v>
       </c>
-      <c r="Y34">
+      <c r="Y56">
         <v>340</v>
       </c>
-      <c r="Z34">
+      <c r="Z56">
         <v>370</v>
       </c>
-      <c r="AA34">
-        <v>370</v>
-      </c>
-      <c r="AB34">
+      <c r="AA56">
+        <v>310</v>
+      </c>
+      <c r="AB56">
         <v>340</v>
       </c>
-      <c r="AC34">
+      <c r="AC56">
         <v>360</v>
       </c>
-      <c r="AD34">
+      <c r="AD56">
         <v>360</v>
       </c>
     </row>
@@ -4081,7 +6124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B795269-CAE1-446B-9C2B-1AE6D53E4204}">
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -4218,7 +6261,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="E7" s="8">
         <v>6</v>
@@ -4238,7 +6281,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="8">
         <v>7</v>
@@ -4258,7 +6301,7 @@
         <v>41</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" s="8">
         <v>8</v>
@@ -4275,10 +6318,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" s="8">
         <v>9</v>
@@ -4295,10 +6338,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8">
         <v>10</v>
@@ -4318,7 +6361,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="8">
         <v>11</v>
@@ -4332,13 +6375,13 @@
         <v>6</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
       <c r="E13" s="8">
         <v>12</v>
@@ -4352,19 +6395,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="E14" s="8">
         <v>13</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4372,19 +6415,19 @@
         <v>6</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="8">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="E15" s="14">
+        <v>14</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4392,19 +6435,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="8">
-        <v>13</v>
+        <v>125</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E16" s="14">
+        <v>15</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4412,19 +6455,19 @@
         <v>6</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="8">
-        <v>13</v>
+        <v>125</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E17" s="14">
+        <v>16</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4432,19 +6475,19 @@
         <v>6</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="8">
-        <v>13</v>
+        <v>125</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" s="14">
+        <v>17</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4452,19 +6495,19 @@
         <v>6</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="8">
-        <v>13</v>
+        <v>131</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="14">
+        <v>18</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4472,19 +6515,19 @@
         <v>6</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="8">
-        <v>13</v>
+        <v>117</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E20" s="14">
+        <v>19</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4492,19 +6535,19 @@
         <v>6</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="8">
-        <v>13</v>
+        <v>140</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E21" s="11">
+        <v>20</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4512,19 +6555,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="8">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" s="11">
+        <v>23</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4532,19 +6575,19 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="8">
-        <v>13</v>
+        <v>125</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E23" s="11">
+        <v>24</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4552,19 +6595,19 @@
         <v>6</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="8">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="11">
+        <v>25</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4572,19 +6615,19 @@
         <v>6</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="8">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E25" s="11">
+        <v>26</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4592,19 +6635,19 @@
         <v>6</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E26" s="8">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" s="11">
+        <v>27</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4612,19 +6655,19 @@
         <v>6</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="8">
-        <v>13</v>
+        <v>36</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="11">
+        <v>28</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4632,19 +6675,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="8">
-        <v>13</v>
+        <v>54</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" s="11">
+        <v>29</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4652,19 +6695,19 @@
         <v>6</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="8">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="E29" s="11">
+        <v>30</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4672,19 +6715,19 @@
         <v>6</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="8">
-        <v>13</v>
+        <v>220</v>
+      </c>
+      <c r="E30" s="11">
+        <v>31</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4692,19 +6735,19 @@
         <v>6</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="8">
-        <v>13</v>
+        <v>221</v>
+      </c>
+      <c r="E31" s="11">
+        <v>32</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4712,19 +6755,19 @@
         <v>6</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="8">
-        <v>13</v>
+        <v>222</v>
+      </c>
+      <c r="E32" s="11">
+        <v>33</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4732,19 +6775,19 @@
         <v>6</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" s="8">
-        <v>13</v>
+        <v>223</v>
+      </c>
+      <c r="E33" s="11">
+        <v>34</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4752,19 +6795,19 @@
         <v>6</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="8">
-        <v>13</v>
+        <v>224</v>
+      </c>
+      <c r="E34" s="11">
+        <v>35</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4772,19 +6815,19 @@
         <v>6</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>103</v>
+        <v>227</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E35" s="8">
-        <v>13</v>
+        <v>225</v>
+      </c>
+      <c r="E35" s="11">
+        <v>36</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4792,19 +6835,19 @@
         <v>6</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>105</v>
-      </c>
       <c r="D36" s="8" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="E36" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4812,19 +6855,19 @@
         <v>6</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E37" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4832,19 +6875,19 @@
         <v>6</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="E38" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4852,19 +6895,19 @@
         <v>6</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="E39" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4872,19 +6915,19 @@
         <v>6</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="E40" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4892,19 +6935,19 @@
         <v>6</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E41" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4912,19 +6955,19 @@
         <v>6</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E42" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4932,19 +6975,19 @@
         <v>6</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="E43" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4952,19 +6995,19 @@
         <v>6</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="E44" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4972,19 +7015,19 @@
         <v>6</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E45" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4992,19 +7035,19 @@
         <v>6</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E46" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5012,19 +7055,19 @@
         <v>6</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="E47" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -5032,19 +7075,19 @@
         <v>6</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="E48" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -5052,19 +7095,19 @@
         <v>6</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="E49" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -5072,19 +7115,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E50" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,19 +7135,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="E51" s="8">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,179 +7155,179 @@
         <v>6</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="D52" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="8">
+        <v>37</v>
+      </c>
+      <c r="F52" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="E52" s="8">
-        <v>13</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="E53" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="E54" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E55" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="E56" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="E57" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="E58" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="E59" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="E60" s="8">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,19 +7335,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="E61" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -5312,19 +7355,19 @@
         <v>6</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="E62" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -5332,19 +7375,19 @@
         <v>6</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="E63" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5352,19 +7395,19 @@
         <v>6</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E64" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5372,19 +7415,19 @@
         <v>6</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="E65" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,19 +7435,19 @@
         <v>6</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="E66" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5412,19 +7455,19 @@
         <v>6</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="E67" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5432,19 +7475,19 @@
         <v>6</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="E68" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5452,19 +7495,19 @@
         <v>6</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="E69" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,19 +7515,19 @@
         <v>6</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="E70" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5492,19 +7535,19 @@
         <v>6</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="E71" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5512,19 +7555,19 @@
         <v>6</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="E72" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5532,19 +7575,19 @@
         <v>6</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>162</v>
+        <v>36</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="E73" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5552,179 +7595,179 @@
         <v>6</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E74" s="8">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="E75" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="E76" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="E77" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>167</v>
+        <v>41</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="E78" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="E79" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="E80" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="E81" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="E82" s="8">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5732,19 +7775,19 @@
         <v>6</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E83" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5752,19 +7795,19 @@
         <v>6</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E84" s="8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5772,19 +7815,19 @@
         <v>6</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C85" t="s">
-        <v>173</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E85" s="9">
-        <v>16</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="8">
+        <v>21</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5792,19 +7835,19 @@
         <v>6</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C86" t="s">
-        <v>174</v>
-      </c>
-      <c r="D86" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E86" s="9">
-        <v>16</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E86" s="8">
+        <v>21</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5812,19 +7855,19 @@
         <v>6</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C87" t="s">
-        <v>175</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E87" s="9">
-        <v>16</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="8">
+        <v>21</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5832,19 +7875,19 @@
         <v>6</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C88" t="s">
-        <v>176</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="9">
-        <v>16</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="8">
+        <v>21</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5852,19 +7895,19 @@
         <v>6</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C89" t="s">
-        <v>177</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="9">
-        <v>16</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="8">
+        <v>21</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5872,19 +7915,19 @@
         <v>6</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C90" t="s">
-        <v>178</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="9">
-        <v>16</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="8">
+        <v>21</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5892,19 +7935,19 @@
         <v>6</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" t="s">
-        <v>179</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E91" s="9">
-        <v>16</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="8">
+        <v>21</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5912,19 +7955,19 @@
         <v>6</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C92" t="s">
-        <v>180</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E92" s="9">
-        <v>16</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="8">
+        <v>21</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5932,19 +7975,19 @@
         <v>6</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C93" t="s">
-        <v>181</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E93" s="9">
-        <v>16</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="8">
+        <v>21</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5952,19 +7995,19 @@
         <v>6</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C94" t="s">
-        <v>182</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="9">
-        <v>16</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="8">
+        <v>21</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5972,19 +8015,19 @@
         <v>6</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C95" t="s">
-        <v>183</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="9">
-        <v>16</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="8">
+        <v>21</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5992,19 +8035,19 @@
         <v>6</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C96" t="s">
-        <v>184</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="9">
-        <v>16</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="8">
+        <v>21</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -6012,279 +8055,1639 @@
         <v>6</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C97" t="s">
-        <v>185</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="9">
-        <v>16</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="8">
+        <v>21</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C98" t="s">
-        <v>173</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E98" s="9">
-        <v>17</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="8">
+        <v>21</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C99" t="s">
-        <v>174</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E99" s="9">
-        <v>17</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E99" s="8">
+        <v>21</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C100" t="s">
-        <v>175</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="9">
-        <v>17</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="8">
+        <v>21</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C101" t="s">
-        <v>176</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E101" s="9">
-        <v>17</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E101" s="8">
+        <v>21</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C102" t="s">
-        <v>177</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="9">
-        <v>17</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="8">
+        <v>21</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C103" t="s">
-        <v>178</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E103" s="9">
-        <v>17</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E103" s="8">
+        <v>21</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C104" t="s">
-        <v>179</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E104" s="9">
-        <v>17</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="8">
+        <v>21</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C105" t="s">
-        <v>180</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E105" s="9">
-        <v>17</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="8">
+        <v>21</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C106" t="s">
-        <v>181</v>
-      </c>
-      <c r="D106" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E106" s="9">
-        <v>17</v>
-      </c>
-      <c r="F106" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E106" s="8">
+        <v>21</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C107" t="s">
-        <v>182</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E107" s="9">
-        <v>17</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E107" s="8">
+        <v>21</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C108" t="s">
-        <v>183</v>
-      </c>
-      <c r="D108" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E108" s="9">
-        <v>17</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" s="8">
+        <v>21</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C109" t="s">
-        <v>184</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E109" s="9">
-        <v>17</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="8">
+        <v>21</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
-        <v>188</v>
+        <v>6</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C110" t="s">
+        <v>147</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" s="8">
+        <v>21</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" s="8">
+        <v>21</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E112" s="8">
+        <v>21</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E113" s="8">
+        <v>21</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="8">
+        <v>21</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="8">
+        <v>21</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="8">
+        <v>21</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="8">
+        <v>21</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="8">
+        <v>21</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="8">
+        <v>21</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="8">
+        <v>21</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E121" s="8">
+        <v>21</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="8">
+        <v>21</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E123" s="8">
+        <v>21</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C124" t="s">
+        <v>170</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E124" s="9">
+        <v>22</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C125" t="s">
+        <v>214</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E125" s="9">
+        <v>22</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C126" t="s">
+        <v>171</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E126" s="9">
+        <v>22</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C127" t="s">
+        <v>172</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="9">
+        <v>22</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C128" t="s">
+        <v>215</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E128" s="9">
+        <v>22</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C129" t="s">
+        <v>173</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E129" s="9">
+        <v>22</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C130" t="s">
+        <v>175</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E130" s="9">
+        <v>22</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C131" t="s">
+        <v>176</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E131" s="9">
+        <v>22</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C132" t="s">
+        <v>177</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E132" s="9">
+        <v>22</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C133" t="s">
+        <v>178</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="9">
+        <v>22</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" t="s">
+        <v>179</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="9">
+        <v>22</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C135" t="s">
+        <v>180</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" s="9">
+        <v>22</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136" t="s">
+        <v>181</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E136" s="9">
+        <v>22</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" t="s">
+        <v>182</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E137" s="9">
+        <v>22</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D110" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E110" s="9">
-        <v>17</v>
-      </c>
-      <c r="F110" s="9" t="s">
+      <c r="B138" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C138" s="8" t="s">
         <v>149</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="8">
+        <v>39</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="8">
+        <v>39</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="8">
+        <v>39</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="8">
+        <v>39</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E142" s="8">
+        <v>39</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="8">
+        <v>39</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E144" s="8">
+        <v>39</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E145" s="8">
+        <v>39</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="8">
+        <v>39</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="8">
+        <v>39</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E148" s="8">
+        <v>39</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="8">
+        <v>39</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="8">
+        <v>39</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E151" s="8">
+        <v>39</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E152" s="8">
+        <v>39</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="8">
+        <v>39</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="8">
+        <v>39</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E155" s="8">
+        <v>39</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E156" s="8">
+        <v>39</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E157" s="8">
+        <v>39</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E158" s="8">
+        <v>39</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="8">
+        <v>39</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E160" s="8">
+        <v>39</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="8">
+        <v>39</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="8">
+        <v>39</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="8">
+        <v>39</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="8">
+        <v>39</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="8">
+        <v>39</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E166" s="8">
+        <v>39</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E167" s="8">
+        <v>39</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E168" s="8">
+        <v>39</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E169" s="8">
+        <v>39</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="8">
+        <v>39</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E171" s="8">
+        <v>39</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E172" s="8">
+        <v>39</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E173" s="8">
+        <v>39</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E174" s="8">
+        <v>39</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E175" s="8">
+        <v>39</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E176" s="8">
+        <v>39</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="8">
+        <v>39</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178" s="8">
+        <v>39</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
